--- a/资料/数飞科技（宁波）-企业基础资料维护.xlsx
+++ b/资料/数飞科技（宁波）-企业基础资料维护.xlsx
@@ -3,18 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator.DESKTOP-U3RMRMG\Desktop\ITSS三级\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21330" windowHeight="12375"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="21330" windowHeight="12375" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -134,33 +130,43 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -168,6 +174,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -176,6 +183,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -184,6 +192,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -192,6 +201,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -200,6 +210,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -208,6 +219,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -215,6 +227,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -223,6 +236,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -231,6 +245,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -239,6 +254,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -246,6 +262,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -254,6 +271,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -261,6 +279,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -268,6 +287,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -275,6 +295,7 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -282,211 +303,207 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,21 +514,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -527,7 +529,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -536,7 +537,6 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -545,7 +545,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -560,7 +559,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -575,7 +573,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -590,7 +587,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -599,7 +595,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -610,200 +605,330 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="55">
+  <cellStyleXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="55">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
-    <cellStyle name="Percent" xfId="50"/>
-    <cellStyle name="Currency" xfId="51"/>
-    <cellStyle name="Currency [0]" xfId="52"/>
-    <cellStyle name="Comma" xfId="53"/>
-    <cellStyle name="Comma [0]" xfId="54"/>
+  <cellStyles count="59">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="千位分隔" xfId="20"/>
+    <cellStyle name="货币" xfId="21"/>
+    <cellStyle name="百分比" xfId="22"/>
+    <cellStyle name="千位分隔[0]" xfId="23"/>
+    <cellStyle name="货币[0]" xfId="24"/>
+    <cellStyle name="超链接" xfId="25"/>
+    <cellStyle name="已访问的超链接" xfId="26"/>
+    <cellStyle name="注释" xfId="27"/>
+    <cellStyle name="警告文本" xfId="28"/>
+    <cellStyle name="标题" xfId="29"/>
+    <cellStyle name="解释性文本" xfId="30"/>
+    <cellStyle name="标题 1" xfId="31"/>
+    <cellStyle name="标题 2" xfId="32"/>
+    <cellStyle name="标题 3" xfId="33"/>
+    <cellStyle name="标题 4" xfId="34"/>
+    <cellStyle name="输入" xfId="35"/>
+    <cellStyle name="输出" xfId="36"/>
+    <cellStyle name="计算" xfId="37"/>
+    <cellStyle name="检查单元格" xfId="38"/>
+    <cellStyle name="链接单元格" xfId="39"/>
+    <cellStyle name="汇总" xfId="40"/>
+    <cellStyle name="好" xfId="41"/>
+    <cellStyle name="差" xfId="42"/>
+    <cellStyle name="适中" xfId="43"/>
+    <cellStyle name="强调文字颜色 1" xfId="44"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
+    <cellStyle name="强调文字颜色 2" xfId="48"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
+    <cellStyle name="强调文字颜色 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
+    <cellStyle name="强调文字颜色 4" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
+    <cellStyle name="强调文字颜色 5" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
+    <cellStyle name="强调文字颜色 6" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
+    <cellStyle name="Percent" xfId="68"/>
+    <cellStyle name="Currency" xfId="69"/>
+    <cellStyle name="Currency [0]" xfId="70"/>
+    <cellStyle name="Comma" xfId="71"/>
+    <cellStyle name="Comma [0]" xfId="72"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -814,7 +939,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -842,36 +967,36 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -886,19 +1011,19 @@
       </font>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -913,59 +1038,59 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79998"/>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -974,7 +1099,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -987,6 +1112,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1244,30 +1437,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A2:H39"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9.26666666666667" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3"/>
-    <col min="2" max="2" width="46.8916666666667" style="4" customWidth="1"/>
+    <col min="2" max="2" width="46.875" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.8833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="1" spans="1:8" ht="14.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
         <v>1</v>
@@ -1279,7 +1488,9 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="14.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
@@ -1295,8 +1506,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A5" s="3"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
@@ -1308,8 +1520,9 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A6" s="3"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1325,8 +1538,9 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A7" s="3"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
@@ -1342,8 +1556,9 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A8" s="3"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
@@ -1359,8 +1574,9 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A9" s="3"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1376,7 +1592,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="6" t="s">
@@ -1394,40 +1610,91 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
     </row>
-    <row r="12" s="1" customFormat="1"/>
-    <row r="13" s="1" customFormat="1" spans="1:8">
+    <row r="11" spans="1:8" ht="14.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" ht="14.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A13" s="3">
         <v>2</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
+    <row r="15" spans="1:8" s="1" customFormat="1" ht="14.25">
       <c r="A15" s="3">
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
-    <row r="16" ht="28.5" spans="1:8">
+    <row r="16" spans="1:8" ht="28.5">
+      <c r="A16" s="3"/>
       <c r="B16" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="230" customHeight="1" spans="1:2">
+    <row r="17" spans="1:8" s="2" customFormat="1" ht="230" customHeight="1">
+      <c r="A17" s="2"/>
       <c r="B17" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="13.5"/>
     <row r="19" s="2" customFormat="1" ht="13.5"/>
-    <row r="20" s="1" customFormat="1" spans="1:2">
+    <row r="20" spans="1:2" s="1" customFormat="1" ht="14.25">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
     </row>
@@ -1448,7 +1715,7 @@
     <mergeCell ref="H4:H10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>